--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484313_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484313_PROCESSED_CHRONO.xlsx
@@ -565,10 +565,10 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>4.8006</v>
+        <v>4.6589</v>
       </c>
       <c r="E2" t="n">
-        <v>3.557</v>
+        <v>3.4153</v>
       </c>
       <c r="F2" t="n">
         <v>1.2436</v>
@@ -610,10 +610,10 @@
         <v>2.1488</v>
       </c>
       <c r="S2" t="n">
-        <v>-0.0467</v>
+        <v>-0.1885</v>
       </c>
       <c r="T2" t="n">
-        <v>0.0221</v>
+        <v>-0.1196</v>
       </c>
       <c r="U2" t="n">
         <v>-0.0689</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>3.2284</v>
+        <v>3.3162</v>
       </c>
       <c r="E3" t="n">
-        <v>3.7267</v>
+        <v>3.7872</v>
       </c>
       <c r="F3" t="n">
-        <v>-0.4983</v>
+        <v>-0.471</v>
       </c>
       <c r="G3" t="n">
         <v>2.4756</v>
@@ -688,13 +688,13 @@
         <v>1.3674</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.6146</v>
+        <v>-0.5269</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.7262999999999999</v>
+        <v>-0.6657</v>
       </c>
       <c r="U3" t="n">
-        <v>0.1117</v>
+        <v>0.1389</v>
       </c>
       <c r="V3" t="n">
         <v>0</v>
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>0.9903</v>
+        <v>1.6865</v>
       </c>
       <c r="E4" t="n">
-        <v>1.3011</v>
+        <v>1.8066</v>
       </c>
       <c r="F4" t="n">
-        <v>-0.3108</v>
+        <v>-0.1202</v>
       </c>
       <c r="G4" t="n">
         <v>1.8123</v>
@@ -766,13 +766,13 @@
         <v>2.7348</v>
       </c>
       <c r="S4" t="n">
-        <v>-2.1895</v>
+        <v>-1.4932</v>
       </c>
       <c r="T4" t="n">
-        <v>-1.1362</v>
+        <v>-0.6306</v>
       </c>
       <c r="U4" t="n">
-        <v>-1.0533</v>
+        <v>-0.8627</v>
       </c>
       <c r="V4" t="n">
         <v>0</v>
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>0.1263</v>
+        <v>0.6379</v>
       </c>
       <c r="E5" t="n">
-        <v>0.2092</v>
+        <v>0.7753</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.083</v>
+        <v>-0.1374</v>
       </c>
       <c r="G5" t="n">
         <v>-0.6793</v>
@@ -844,13 +844,13 @@
         <v>3.1255</v>
       </c>
       <c r="S5" t="n">
-        <v>-1.3432</v>
+        <v>-0.8316</v>
       </c>
       <c r="T5" t="n">
-        <v>-1.1362</v>
+        <v>-0.5701000000000001</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.207</v>
+        <v>-0.2615</v>
       </c>
       <c r="V5" t="n">
         <v>0</v>
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.2138</v>
+        <v>-1.1879</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.0726</v>
+        <v>-0.7199</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.1412</v>
+        <v>-0.468</v>
       </c>
       <c r="G6" t="n">
         <v>-0.9186</v>
@@ -922,13 +922,13 @@
         <v>3.1255</v>
       </c>
       <c r="S6" t="n">
-        <v>0.6845</v>
+        <v>-0.2896</v>
       </c>
       <c r="T6" t="n">
-        <v>0.1983</v>
+        <v>-0.449</v>
       </c>
       <c r="U6" t="n">
-        <v>0.4863</v>
+        <v>0.1594</v>
       </c>
       <c r="V6" t="n">
         <v>-2.7145</v>
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-1.605</v>
+        <v>-1.3483</v>
       </c>
       <c r="E7" t="n">
-        <v>-1.2504</v>
+        <v>-1.0482</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.3546</v>
+        <v>-0.3001</v>
       </c>
       <c r="G7" t="n">
         <v>-1.6161</v>
@@ -1000,13 +1000,13 @@
         <v>1.7581</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.8056</v>
+        <v>-0.5489000000000001</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.4704</v>
+        <v>-0.2682</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.3352</v>
+        <v>-0.2807</v>
       </c>
       <c r="V7" t="n">
         <v>-0.9414</v>
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-2.136</v>
+        <v>-1.9804</v>
       </c>
       <c r="E8" t="n">
-        <v>-1.8</v>
+        <v>-1.6989</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.336</v>
+        <v>-0.2815</v>
       </c>
       <c r="G8" t="n">
         <v>-0.4885</v>
@@ -1078,13 +1078,13 @@
         <v>0.586</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.0847</v>
+        <v>0.0709</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.121</v>
+        <v>-0.0199</v>
       </c>
       <c r="U8" t="n">
-        <v>0.0363</v>
+        <v>0.09080000000000001</v>
       </c>
       <c r="V8" t="n">
         <v>0</v>
@@ -1099,7 +1099,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>J. CALLAVE FERRER</t>
+          <t>J. SALAVEDRA VILARNAU</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,73 +1111,73 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-3.3585</v>
+        <v>-3.1356</v>
       </c>
       <c r="E9" t="n">
-        <v>-1.3129</v>
+        <v>-0.4802</v>
       </c>
       <c r="F9" t="n">
-        <v>-2.0456</v>
+        <v>-2.6554</v>
       </c>
       <c r="G9" t="n">
-        <v>-1.5363</v>
+        <v>-1.3832</v>
       </c>
       <c r="H9" t="n">
-        <v>-1.2003</v>
+        <v>-0.8163</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.336</v>
+        <v>-0.5669</v>
       </c>
       <c r="J9" t="n">
-        <v>-0.098</v>
+        <v>0.9386</v>
       </c>
       <c r="K9" t="n">
-        <v>-0.5718</v>
+        <v>0.6958</v>
       </c>
       <c r="L9" t="n">
-        <v>0.4737</v>
+        <v>0.2428</v>
       </c>
       <c r="M9" t="n">
-        <v>-1.4382</v>
+        <v>-2.3219</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.6284999999999999</v>
+        <v>-1.5121</v>
       </c>
       <c r="O9" t="n">
         <v>-0.8097</v>
       </c>
       <c r="P9" t="n">
-        <v>-1.7581</v>
+        <v>0.3907</v>
       </c>
       <c r="Q9" t="n">
-        <v>-3.1255</v>
+        <v>-1.1721</v>
       </c>
       <c r="R9" t="n">
-        <v>1.3674</v>
+        <v>1.5627</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.6735</v>
+        <v>-0.9244</v>
       </c>
       <c r="T9" t="n">
-        <v>0.08260000000000001</v>
+        <v>-0.524</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.7561</v>
+        <v>-0.4004</v>
       </c>
       <c r="V9" t="n">
-        <v>0.6093</v>
+        <v>-1.2186</v>
       </c>
       <c r="W9" t="n">
-        <v>1.8279</v>
+        <v>0.2772</v>
       </c>
       <c r="X9" t="n">
-        <v>-1.2186</v>
+        <v>-1.4959</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>F. DIAZ CABANAS</t>
+          <t>J. CALLAVE FERRER</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,73 +1189,73 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-3.365</v>
+        <v>-3.4712</v>
       </c>
       <c r="E10" t="n">
-        <v>-2.9823</v>
+        <v>-1.6163</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.3826</v>
+        <v>-1.8549</v>
       </c>
       <c r="G10" t="n">
-        <v>-4.7591</v>
+        <v>-1.5363</v>
       </c>
       <c r="H10" t="n">
-        <v>-2.4533</v>
+        <v>-1.2003</v>
       </c>
       <c r="I10" t="n">
-        <v>-2.3058</v>
+        <v>-0.336</v>
       </c>
       <c r="J10" t="n">
-        <v>-3.5957</v>
+        <v>-0.098</v>
       </c>
       <c r="K10" t="n">
-        <v>-1.6948</v>
+        <v>-0.5718</v>
       </c>
       <c r="L10" t="n">
-        <v>-1.9009</v>
+        <v>0.4737</v>
       </c>
       <c r="M10" t="n">
-        <v>-1.1634</v>
+        <v>-1.4382</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.7585</v>
+        <v>-0.6284999999999999</v>
       </c>
       <c r="O10" t="n">
-        <v>-0.4049</v>
+        <v>-0.8097</v>
       </c>
       <c r="P10" t="n">
-        <v>0.7814</v>
+        <v>-1.7581</v>
       </c>
       <c r="Q10" t="n">
-        <v>0</v>
+        <v>-3.1255</v>
       </c>
       <c r="R10" t="n">
-        <v>0.7814</v>
+        <v>1.3674</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.6059</v>
+        <v>-0.7862</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.6052</v>
+        <v>-0.2207</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.0005999999999999999</v>
+        <v>-0.5655</v>
       </c>
       <c r="V10" t="n">
-        <v>1.2186</v>
+        <v>0.6093</v>
       </c>
       <c r="W10" t="n">
-        <v>1.2186</v>
+        <v>1.8279</v>
       </c>
       <c r="X10" t="n">
-        <v>0</v>
+        <v>-1.2186</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>J. SALAVEDRA VILARNAU</t>
+          <t>F. DIAZ CABANAS</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,67 +1267,67 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-3.3651</v>
+        <v>-3.5556</v>
       </c>
       <c r="E11" t="n">
-        <v>-0.6825</v>
+        <v>-2.9823</v>
       </c>
       <c r="F11" t="n">
-        <v>-2.6826</v>
+        <v>-0.5733</v>
       </c>
       <c r="G11" t="n">
-        <v>-1.3832</v>
+        <v>-4.7591</v>
       </c>
       <c r="H11" t="n">
-        <v>-0.8163</v>
+        <v>-2.4533</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.5669</v>
+        <v>-2.3058</v>
       </c>
       <c r="J11" t="n">
-        <v>0.9386</v>
+        <v>-3.5957</v>
       </c>
       <c r="K11" t="n">
-        <v>0.6958</v>
+        <v>-1.6948</v>
       </c>
       <c r="L11" t="n">
-        <v>0.2428</v>
+        <v>-1.9009</v>
       </c>
       <c r="M11" t="n">
-        <v>-2.3219</v>
+        <v>-1.1634</v>
       </c>
       <c r="N11" t="n">
-        <v>-1.5121</v>
+        <v>-0.7585</v>
       </c>
       <c r="O11" t="n">
-        <v>-0.8097</v>
+        <v>-0.4049</v>
       </c>
       <c r="P11" t="n">
-        <v>0.3907</v>
+        <v>0.7814</v>
       </c>
       <c r="Q11" t="n">
-        <v>-1.1721</v>
+        <v>0</v>
       </c>
       <c r="R11" t="n">
-        <v>1.5627</v>
+        <v>0.7814</v>
       </c>
       <c r="S11" t="n">
-        <v>-1.1539</v>
+        <v>-0.7965</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.7262999999999999</v>
+        <v>-0.6052</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.4276</v>
+        <v>-0.1913</v>
       </c>
       <c r="V11" t="n">
-        <v>-1.2186</v>
+        <v>1.2186</v>
       </c>
       <c r="W11" t="n">
-        <v>0.2772</v>
+        <v>1.2186</v>
       </c>
       <c r="X11" t="n">
-        <v>-1.4959</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12">
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-4.824</v>
+        <v>-5.0395</v>
       </c>
       <c r="E12" t="n">
-        <v>-1.76</v>
+        <v>-2.0028</v>
       </c>
       <c r="F12" t="n">
-        <v>-3.064</v>
+        <v>-3.0367</v>
       </c>
       <c r="G12" t="n">
         <v>-2.639</v>
@@ -1390,13 +1390,13 @@
         <v>0.9767</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.5403</v>
+        <v>-0.7559</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.1127</v>
+        <v>-0.3555</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.4276</v>
+        <v>-0.4004</v>
       </c>
       <c r="V12" t="n">
         <v>-0.2772</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-9.7218</v>
+        <v>-9.419</v>
       </c>
       <c r="E13" t="n">
-        <v>-1.0667</v>
+        <v>-0.7642000000000007</v>
       </c>
       <c r="F13" t="n">
-        <v>-8.655099999999999</v>
+        <v>-8.6549</v>
       </c>
       <c r="G13" t="n">
         <v>-5.439299999999999</v>
@@ -1459,7 +1459,7 @@
         <v>-5.3998</v>
       </c>
       <c r="P13" t="n">
-        <v>5.860399999999998</v>
+        <v>5.860399999999999</v>
       </c>
       <c r="Q13" t="n">
         <v>-13.6741</v>
@@ -1468,19 +1468,19 @@
         <v>19.5343</v>
       </c>
       <c r="S13" t="n">
-        <v>-7.3734</v>
+        <v>-7.0708</v>
       </c>
       <c r="T13" t="n">
-        <v>-4.731300000000001</v>
+        <v>-4.428500000000001</v>
       </c>
       <c r="U13" t="n">
-        <v>-2.642</v>
+        <v>-2.6423</v>
       </c>
       <c r="V13" t="n">
-        <v>-2.7693</v>
+        <v>-2.769299999999999</v>
       </c>
       <c r="W13" t="n">
-        <v>5.6512</v>
+        <v>5.651200000000001</v>
       </c>
       <c r="X13" t="n">
         <v>-8.4206</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>6.173</v>
+        <v>5.5105</v>
       </c>
       <c r="E14" t="n">
-        <v>6.1123</v>
+        <v>5.5056</v>
       </c>
       <c r="F14" t="n">
-        <v>0.0607</v>
+        <v>0.0049</v>
       </c>
       <c r="G14" t="n">
         <v>2.6671</v>
@@ -1546,13 +1546,13 @@
         <v>2.5395</v>
       </c>
       <c r="S14" t="n">
-        <v>2.3105</v>
+        <v>1.648</v>
       </c>
       <c r="T14" t="n">
-        <v>1.3703</v>
+        <v>0.7635999999999999</v>
       </c>
       <c r="U14" t="n">
-        <v>0.9402</v>
+        <v>0.8844</v>
       </c>
       <c r="V14" t="n">
         <v>0.6093</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>3.823</v>
+        <v>2.9116</v>
       </c>
       <c r="E15" t="n">
-        <v>2.2347</v>
+        <v>1.3247</v>
       </c>
       <c r="F15" t="n">
-        <v>1.5883</v>
+        <v>1.5869</v>
       </c>
       <c r="G15" t="n">
         <v>1.0504</v>
@@ -1624,13 +1624,13 @@
         <v>1.3674</v>
       </c>
       <c r="S15" t="n">
-        <v>2.1047</v>
+        <v>1.1933</v>
       </c>
       <c r="T15" t="n">
-        <v>1.794</v>
+        <v>0.8839</v>
       </c>
       <c r="U15" t="n">
-        <v>0.3108</v>
+        <v>0.3094</v>
       </c>
       <c r="V15" t="n">
         <v>0.2772</v>
@@ -1645,7 +1645,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>M. CASADO FAJO</t>
+          <t>D. FLOREN LARIO</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,73 +1657,73 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>1.1321</v>
+        <v>1.8554</v>
       </c>
       <c r="E16" t="n">
-        <v>-0.7311</v>
+        <v>0.4807</v>
       </c>
       <c r="F16" t="n">
-        <v>1.8632</v>
+        <v>1.3747</v>
       </c>
       <c r="G16" t="n">
-        <v>-1.0229</v>
+        <v>-0.3128</v>
       </c>
       <c r="H16" t="n">
-        <v>-1.7105</v>
+        <v>-0.8788</v>
       </c>
       <c r="I16" t="n">
-        <v>0.6875</v>
+        <v>0.5659</v>
       </c>
       <c r="J16" t="n">
-        <v>0.4305</v>
+        <v>-0.3677</v>
       </c>
       <c r="K16" t="n">
-        <v>-0.2584</v>
+        <v>-0.5296</v>
       </c>
       <c r="L16" t="n">
-        <v>0.6889</v>
+        <v>0.1619</v>
       </c>
       <c r="M16" t="n">
-        <v>-1.4534</v>
+        <v>0.0549</v>
       </c>
       <c r="N16" t="n">
-        <v>-1.452</v>
+        <v>-0.3492</v>
       </c>
       <c r="O16" t="n">
-        <v>-0.0014</v>
+        <v>0.4041</v>
       </c>
       <c r="P16" t="n">
-        <v>0.3907</v>
+        <v>-0.3907</v>
       </c>
       <c r="Q16" t="n">
         <v>-1.9534</v>
       </c>
       <c r="R16" t="n">
-        <v>2.3441</v>
+        <v>1.5627</v>
       </c>
       <c r="S16" t="n">
-        <v>1.4323</v>
+        <v>0.3989</v>
       </c>
       <c r="T16" t="n">
-        <v>0.5147</v>
+        <v>0.3646</v>
       </c>
       <c r="U16" t="n">
-        <v>0.9176</v>
+        <v>0.0343</v>
       </c>
       <c r="V16" t="n">
-        <v>0.3321</v>
+        <v>2.16</v>
       </c>
       <c r="W16" t="n">
-        <v>0.2772</v>
+        <v>2.4373</v>
       </c>
       <c r="X16" t="n">
-        <v>0.0549</v>
+        <v>-0.2772</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>D. FLOREN LARIO</t>
+          <t>P. CABAÑERO PUERTAS</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,73 +1735,73 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>1.0322</v>
+        <v>1.4652</v>
       </c>
       <c r="E17" t="n">
-        <v>-0.126</v>
+        <v>1.5345</v>
       </c>
       <c r="F17" t="n">
-        <v>1.1582</v>
+        <v>-0.0693</v>
       </c>
       <c r="G17" t="n">
-        <v>-0.3128</v>
+        <v>1.3048</v>
       </c>
       <c r="H17" t="n">
-        <v>-0.8788</v>
+        <v>0.9414</v>
       </c>
       <c r="I17" t="n">
-        <v>0.5659</v>
+        <v>0.3634</v>
       </c>
       <c r="J17" t="n">
-        <v>-0.3677</v>
+        <v>3.3578</v>
       </c>
       <c r="K17" t="n">
-        <v>-0.5296</v>
+        <v>2.0491</v>
       </c>
       <c r="L17" t="n">
-        <v>0.1619</v>
+        <v>1.3087</v>
       </c>
       <c r="M17" t="n">
-        <v>0.0549</v>
+        <v>-2.053</v>
       </c>
       <c r="N17" t="n">
-        <v>-0.3492</v>
+        <v>-1.1077</v>
       </c>
       <c r="O17" t="n">
-        <v>0.4041</v>
+        <v>-0.9453</v>
       </c>
       <c r="P17" t="n">
-        <v>-0.3907</v>
+        <v>0</v>
       </c>
       <c r="Q17" t="n">
         <v>-1.9534</v>
       </c>
       <c r="R17" t="n">
-        <v>1.5627</v>
+        <v>1.9534</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.4243</v>
+        <v>0.7697000000000001</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.2421</v>
+        <v>0.1301</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.1822</v>
+        <v>0.6395999999999999</v>
       </c>
       <c r="V17" t="n">
-        <v>2.16</v>
+        <v>-0.6093</v>
       </c>
       <c r="W17" t="n">
-        <v>2.4373</v>
+        <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>-0.2772</v>
+        <v>-0.6093</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>L. PERALTA VISTUE</t>
+          <t>M. CASADO FAJO</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,73 +1813,73 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>0.778</v>
+        <v>1.3953</v>
       </c>
       <c r="E18" t="n">
-        <v>1.1817</v>
+        <v>-0.63</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.4038</v>
+        <v>2.0253</v>
       </c>
       <c r="G18" t="n">
-        <v>1.5214</v>
+        <v>-1.0229</v>
       </c>
       <c r="H18" t="n">
-        <v>0.4694</v>
+        <v>-1.7105</v>
       </c>
       <c r="I18" t="n">
-        <v>1.0519</v>
+        <v>0.6875</v>
       </c>
       <c r="J18" t="n">
-        <v>2.8847</v>
+        <v>0.4305</v>
       </c>
       <c r="K18" t="n">
-        <v>1.0233</v>
+        <v>-0.2584</v>
       </c>
       <c r="L18" t="n">
-        <v>1.8614</v>
+        <v>0.6889</v>
       </c>
       <c r="M18" t="n">
-        <v>-1.3634</v>
+        <v>-1.4534</v>
       </c>
       <c r="N18" t="n">
-        <v>-0.5538</v>
+        <v>-1.452</v>
       </c>
       <c r="O18" t="n">
-        <v>-0.8095</v>
+        <v>-0.0014</v>
       </c>
       <c r="P18" t="n">
-        <v>-1.5627</v>
+        <v>0.3907</v>
       </c>
       <c r="Q18" t="n">
         <v>-1.9534</v>
       </c>
       <c r="R18" t="n">
-        <v>0.3907</v>
+        <v>2.3441</v>
       </c>
       <c r="S18" t="n">
-        <v>0.8194</v>
+        <v>1.6955</v>
       </c>
       <c r="T18" t="n">
-        <v>0.2504</v>
+        <v>0.6158</v>
       </c>
       <c r="U18" t="n">
-        <v>0.5689</v>
+        <v>1.0797</v>
       </c>
       <c r="V18" t="n">
-        <v>0</v>
+        <v>0.3321</v>
       </c>
       <c r="W18" t="n">
-        <v>0</v>
+        <v>0.2772</v>
       </c>
       <c r="X18" t="n">
-        <v>0</v>
+        <v>0.0549</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>P. CABAÑERO PUERTAS</t>
+          <t>L. PERALTA VISTUE</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,67 +1891,67 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>0.6185</v>
+        <v>0.6224</v>
       </c>
       <c r="E19" t="n">
-        <v>1.2312</v>
+        <v>1.0806</v>
       </c>
       <c r="F19" t="n">
-        <v>-0.6127</v>
+        <v>-0.4582</v>
       </c>
       <c r="G19" t="n">
-        <v>1.3048</v>
+        <v>1.5214</v>
       </c>
       <c r="H19" t="n">
-        <v>0.9414</v>
+        <v>0.4694</v>
       </c>
       <c r="I19" t="n">
-        <v>0.3634</v>
+        <v>1.0519</v>
       </c>
       <c r="J19" t="n">
-        <v>3.3578</v>
+        <v>2.8847</v>
       </c>
       <c r="K19" t="n">
-        <v>2.0491</v>
+        <v>1.0233</v>
       </c>
       <c r="L19" t="n">
-        <v>1.3087</v>
+        <v>1.8614</v>
       </c>
       <c r="M19" t="n">
-        <v>-2.053</v>
+        <v>-1.3634</v>
       </c>
       <c r="N19" t="n">
-        <v>-1.1077</v>
+        <v>-0.5538</v>
       </c>
       <c r="O19" t="n">
-        <v>-0.9453</v>
+        <v>-0.8095</v>
       </c>
       <c r="P19" t="n">
-        <v>0</v>
+        <v>-1.5627</v>
       </c>
       <c r="Q19" t="n">
         <v>-1.9534</v>
       </c>
       <c r="R19" t="n">
-        <v>1.9534</v>
+        <v>0.3907</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.077</v>
+        <v>0.6637999999999999</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.1732</v>
+        <v>0.1493</v>
       </c>
       <c r="U19" t="n">
-        <v>0.09619999999999999</v>
+        <v>0.5144</v>
       </c>
       <c r="V19" t="n">
-        <v>-0.6093</v>
+        <v>0</v>
       </c>
       <c r="W19" t="n">
         <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>-0.6093</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>0.2347</v>
+        <v>0.4485</v>
       </c>
       <c r="E20" t="n">
-        <v>0.8668</v>
+        <v>1.2713</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.6321</v>
+        <v>-0.8228</v>
       </c>
       <c r="G20" t="n">
         <v>1.0708</v>
@@ -2014,13 +2014,13 @@
         <v>1.3674</v>
       </c>
       <c r="S20" t="n">
-        <v>0.269</v>
+        <v>0.4828</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.4704</v>
+        <v>-0.0659</v>
       </c>
       <c r="U20" t="n">
-        <v>0.7393999999999999</v>
+        <v>0.5488</v>
       </c>
       <c r="V20" t="n">
         <v>-1.4959</v>
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.3629</v>
+        <v>-0.6934</v>
       </c>
       <c r="E21" t="n">
-        <v>-0.1631</v>
+        <v>-0.4664</v>
       </c>
       <c r="F21" t="n">
-        <v>-0.1998</v>
+        <v>-0.227</v>
       </c>
       <c r="G21" t="n">
         <v>0.5918</v>
@@ -2092,13 +2092,13 @@
         <v>1.3674</v>
       </c>
       <c r="S21" t="n">
-        <v>0.8237</v>
+        <v>0.4932</v>
       </c>
       <c r="T21" t="n">
-        <v>0.0083</v>
+        <v>-0.295</v>
       </c>
       <c r="U21" t="n">
-        <v>0.8154</v>
+        <v>0.7882</v>
       </c>
       <c r="V21" t="n">
         <v>2.7145</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-3.7069</v>
+        <v>-3.1196</v>
       </c>
       <c r="E22" t="n">
-        <v>-1.9516</v>
+        <v>-1.446</v>
       </c>
       <c r="F22" t="n">
-        <v>-1.7553</v>
+        <v>-1.6736</v>
       </c>
       <c r="G22" t="n">
         <v>-1.4312</v>
@@ -2170,13 +2170,13 @@
         <v>0.7814</v>
       </c>
       <c r="S22" t="n">
-        <v>0.115</v>
+        <v>0.7023</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.4099</v>
+        <v>0.09569999999999999</v>
       </c>
       <c r="U22" t="n">
-        <v>0.5249</v>
+        <v>0.6066</v>
       </c>
       <c r="V22" t="n">
         <v>-1.2186</v>
@@ -2203,22 +2203,22 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>9.721699999999998</v>
+        <v>10.3959</v>
       </c>
       <c r="E23" t="n">
-        <v>8.654900000000001</v>
+        <v>8.655000000000001</v>
       </c>
       <c r="F23" t="n">
-        <v>1.0667</v>
+        <v>1.7409</v>
       </c>
       <c r="G23" t="n">
-        <v>5.439399999999999</v>
+        <v>5.439400000000001</v>
       </c>
       <c r="H23" t="n">
         <v>2.744800000000001</v>
       </c>
       <c r="I23" t="n">
-        <v>2.6944</v>
+        <v>2.694400000000001</v>
       </c>
       <c r="J23" t="n">
         <v>17.1264</v>
@@ -2239,7 +2239,7 @@
         <v>-2.7052</v>
       </c>
       <c r="P23" t="n">
-        <v>-5.860299999999999</v>
+        <v>-5.860300000000001</v>
       </c>
       <c r="Q23" t="n">
         <v>-19.5341</v>
@@ -2248,22 +2248,22 @@
         <v>13.674</v>
       </c>
       <c r="S23" t="n">
-        <v>7.3733</v>
+        <v>8.047499999999999</v>
       </c>
       <c r="T23" t="n">
         <v>2.6421</v>
       </c>
       <c r="U23" t="n">
-        <v>4.7312</v>
+        <v>5.4054</v>
       </c>
       <c r="V23" t="n">
-        <v>2.7693</v>
+        <v>2.769300000000001</v>
       </c>
       <c r="W23" t="n">
         <v>8.4207</v>
       </c>
       <c r="X23" t="n">
-        <v>-5.651300000000001</v>
+        <v>-5.651299999999999</v>
       </c>
     </row>
   </sheetData>

--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484313_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484313_PROCESSED_CHRONO.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X23"/>
+  <dimension ref="A1:Y25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -549,6 +549,11 @@
           <t>Def_FT</t>
         </is>
       </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>Game_File</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -627,6 +632,11 @@
       <c r="X2" t="n">
         <v>-0.2772</v>
       </c>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>play_by_play_2484313_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -705,6 +715,11 @@
       <c r="X3" t="n">
         <v>0</v>
       </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>play_by_play_2484313_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -783,6 +798,11 @@
       <c r="X4" t="n">
         <v>0</v>
       </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>play_by_play_2484313_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -861,6 +881,11 @@
       <c r="X5" t="n">
         <v>-1.2186</v>
       </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>play_by_play_2484313_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -939,6 +964,11 @@
       <c r="X6" t="n">
         <v>-2.7145</v>
       </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>play_by_play_2484313_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1017,6 +1047,11 @@
       <c r="X7" t="n">
         <v>-1.2186</v>
       </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>play_by_play_2484313_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -1095,6 +1130,11 @@
       <c r="X8" t="n">
         <v>0</v>
       </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>play_by_play_2484313_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1173,6 +1213,11 @@
       <c r="X9" t="n">
         <v>-1.4959</v>
       </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>play_by_play_2484313_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1251,6 +1296,11 @@
       <c r="X10" t="n">
         <v>-1.2186</v>
       </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>play_by_play_2484313_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1329,6 +1379,11 @@
       <c r="X11" t="n">
         <v>0</v>
       </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>play_by_play_2484313_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1407,6 +1462,11 @@
       <c r="X12" t="n">
         <v>-0.2772</v>
       </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>play_by_play_2484313_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -1485,6 +1545,7 @@
       <c r="X13" t="n">
         <v>-8.4206</v>
       </c>
+      <c r="Y13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -1563,11 +1624,16 @@
       <c r="X14" t="n">
         <v>-2.1052</v>
       </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>play_by_play_2484313_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>R. BORGES PINO</t>
+          <t>P. CABAÑERO PUERTAS</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,73 +1645,78 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>2.9116</v>
+        <v>3.0489</v>
       </c>
       <c r="E15" t="n">
-        <v>1.3247</v>
+        <v>3.0489</v>
       </c>
       <c r="F15" t="n">
-        <v>1.5869</v>
+        <v>0</v>
       </c>
       <c r="G15" t="n">
-        <v>1.0504</v>
+        <v>3.0489</v>
       </c>
       <c r="H15" t="n">
-        <v>0.9967</v>
+        <v>1.2279</v>
       </c>
       <c r="I15" t="n">
-        <v>0.0537</v>
+        <v>1.821</v>
       </c>
       <c r="J15" t="n">
-        <v>1.1402</v>
+        <v>3.0489</v>
       </c>
       <c r="K15" t="n">
-        <v>1.7601</v>
+        <v>1.2279</v>
       </c>
       <c r="L15" t="n">
-        <v>-0.6198</v>
+        <v>1.821</v>
       </c>
       <c r="M15" t="n">
-        <v>-0.0898</v>
+        <v>0</v>
       </c>
       <c r="N15" t="n">
-        <v>-0.7634</v>
+        <v>0</v>
       </c>
       <c r="O15" t="n">
-        <v>0.6735</v>
+        <v>0</v>
       </c>
       <c r="P15" t="n">
-        <v>0.3907</v>
+        <v>0</v>
       </c>
       <c r="Q15" t="n">
-        <v>-0.9767</v>
+        <v>0</v>
       </c>
       <c r="R15" t="n">
-        <v>1.3674</v>
+        <v>0</v>
       </c>
       <c r="S15" t="n">
-        <v>1.1933</v>
+        <v>0</v>
       </c>
       <c r="T15" t="n">
-        <v>0.8839</v>
+        <v>0</v>
       </c>
       <c r="U15" t="n">
-        <v>0.3094</v>
+        <v>0</v>
       </c>
       <c r="V15" t="n">
-        <v>0.2772</v>
+        <v>0</v>
       </c>
       <c r="W15" t="n">
-        <v>0.2772</v>
+        <v>0</v>
       </c>
       <c r="X15" t="n">
         <v>0</v>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>play_by_play_2484313_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>D. FLOREN LARIO</t>
+          <t>R. BORGES PINO</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,73 +1728,78 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>1.8554</v>
+        <v>2.9116</v>
       </c>
       <c r="E16" t="n">
-        <v>0.4807</v>
+        <v>1.3247</v>
       </c>
       <c r="F16" t="n">
-        <v>1.3747</v>
+        <v>1.5869</v>
       </c>
       <c r="G16" t="n">
-        <v>-0.3128</v>
+        <v>1.0504</v>
       </c>
       <c r="H16" t="n">
-        <v>-0.8788</v>
+        <v>0.9967</v>
       </c>
       <c r="I16" t="n">
-        <v>0.5659</v>
+        <v>0.0537</v>
       </c>
       <c r="J16" t="n">
-        <v>-0.3677</v>
+        <v>1.1402</v>
       </c>
       <c r="K16" t="n">
-        <v>-0.5296</v>
+        <v>1.7601</v>
       </c>
       <c r="L16" t="n">
-        <v>0.1619</v>
+        <v>-0.6198</v>
       </c>
       <c r="M16" t="n">
-        <v>0.0549</v>
+        <v>-0.0898</v>
       </c>
       <c r="N16" t="n">
-        <v>-0.3492</v>
+        <v>-0.7634</v>
       </c>
       <c r="O16" t="n">
-        <v>0.4041</v>
+        <v>0.6735</v>
       </c>
       <c r="P16" t="n">
-        <v>-0.3907</v>
+        <v>0.3907</v>
       </c>
       <c r="Q16" t="n">
-        <v>-1.9534</v>
+        <v>-0.9767</v>
       </c>
       <c r="R16" t="n">
-        <v>1.5627</v>
+        <v>1.3674</v>
       </c>
       <c r="S16" t="n">
-        <v>0.3989</v>
+        <v>1.1933</v>
       </c>
       <c r="T16" t="n">
-        <v>0.3646</v>
+        <v>0.8839</v>
       </c>
       <c r="U16" t="n">
-        <v>0.0343</v>
+        <v>0.3094</v>
       </c>
       <c r="V16" t="n">
-        <v>2.16</v>
+        <v>0.2772</v>
       </c>
       <c r="W16" t="n">
-        <v>2.4373</v>
+        <v>0.2772</v>
       </c>
       <c r="X16" t="n">
-        <v>-0.2772</v>
+        <v>0</v>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>play_by_play_2484313_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>P. CABAÑERO PUERTAS</t>
+          <t>D. FLOREN LARIO</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,67 +1811,72 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>1.4652</v>
+        <v>1.8554</v>
       </c>
       <c r="E17" t="n">
-        <v>1.5345</v>
+        <v>0.4807</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.0693</v>
+        <v>1.3747</v>
       </c>
       <c r="G17" t="n">
-        <v>1.3048</v>
+        <v>-0.3128</v>
       </c>
       <c r="H17" t="n">
-        <v>0.9414</v>
+        <v>-0.8788</v>
       </c>
       <c r="I17" t="n">
-        <v>0.3634</v>
+        <v>0.5659</v>
       </c>
       <c r="J17" t="n">
-        <v>3.3578</v>
+        <v>-0.3677</v>
       </c>
       <c r="K17" t="n">
-        <v>2.0491</v>
+        <v>-0.5296</v>
       </c>
       <c r="L17" t="n">
-        <v>1.3087</v>
+        <v>0.1619</v>
       </c>
       <c r="M17" t="n">
-        <v>-2.053</v>
+        <v>0.0549</v>
       </c>
       <c r="N17" t="n">
-        <v>-1.1077</v>
+        <v>-0.3492</v>
       </c>
       <c r="O17" t="n">
-        <v>-0.9453</v>
+        <v>0.4041</v>
       </c>
       <c r="P17" t="n">
-        <v>0</v>
+        <v>-0.3907</v>
       </c>
       <c r="Q17" t="n">
         <v>-1.9534</v>
       </c>
       <c r="R17" t="n">
-        <v>1.9534</v>
+        <v>1.5627</v>
       </c>
       <c r="S17" t="n">
-        <v>0.7697000000000001</v>
+        <v>0.3989</v>
       </c>
       <c r="T17" t="n">
-        <v>0.1301</v>
+        <v>0.3646</v>
       </c>
       <c r="U17" t="n">
-        <v>0.6395999999999999</v>
+        <v>0.0343</v>
       </c>
       <c r="V17" t="n">
-        <v>-0.6093</v>
+        <v>2.16</v>
       </c>
       <c r="W17" t="n">
-        <v>0</v>
+        <v>2.4373</v>
       </c>
       <c r="X17" t="n">
-        <v>-0.6093</v>
+        <v>-0.2772</v>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>play_by_play_2484313_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="18">
@@ -1875,6 +1956,11 @@
       <c r="X18" t="n">
         <v>0.0549</v>
       </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>play_by_play_2484313_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -1953,6 +2039,11 @@
       <c r="X19" t="n">
         <v>0</v>
       </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>play_by_play_2484313_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -2031,6 +2122,11 @@
       <c r="X20" t="n">
         <v>-1.4959</v>
       </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>play_by_play_2484313_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -2047,73 +2143,78 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.6934</v>
+        <v>0.307</v>
       </c>
       <c r="E21" t="n">
-        <v>-0.4664</v>
+        <v>0.307</v>
       </c>
       <c r="F21" t="n">
-        <v>-0.227</v>
+        <v>0</v>
       </c>
       <c r="G21" t="n">
-        <v>0.5918</v>
+        <v>0.307</v>
       </c>
       <c r="H21" t="n">
-        <v>1.4554</v>
+        <v>0.307</v>
       </c>
       <c r="I21" t="n">
-        <v>-0.8636</v>
+        <v>0</v>
       </c>
       <c r="J21" t="n">
-        <v>2.9744</v>
+        <v>0.307</v>
       </c>
       <c r="K21" t="n">
-        <v>2.3536</v>
+        <v>0.307</v>
       </c>
       <c r="L21" t="n">
-        <v>0.6208</v>
+        <v>0</v>
       </c>
       <c r="M21" t="n">
-        <v>-2.3826</v>
+        <v>0</v>
       </c>
       <c r="N21" t="n">
-        <v>-0.8982</v>
+        <v>0</v>
       </c>
       <c r="O21" t="n">
-        <v>-1.4844</v>
+        <v>0</v>
       </c>
       <c r="P21" t="n">
-        <v>-4.4929</v>
+        <v>0</v>
       </c>
       <c r="Q21" t="n">
-        <v>-5.8603</v>
+        <v>0</v>
       </c>
       <c r="R21" t="n">
-        <v>1.3674</v>
+        <v>0</v>
       </c>
       <c r="S21" t="n">
-        <v>0.4932</v>
+        <v>0</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.295</v>
+        <v>0</v>
       </c>
       <c r="U21" t="n">
-        <v>0.7882</v>
+        <v>0</v>
       </c>
       <c r="V21" t="n">
-        <v>2.7145</v>
+        <v>0</v>
       </c>
       <c r="W21" t="n">
-        <v>2.7145</v>
+        <v>0</v>
       </c>
       <c r="X21" t="n">
         <v>0</v>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>play_by_play_2484313_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>F. VIDAL RAMOS</t>
+          <t>J. CASTELLO LOGRONO</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,73 +2226,78 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-3.1196</v>
+        <v>-1.0004</v>
       </c>
       <c r="E22" t="n">
-        <v>-1.446</v>
+        <v>-0.7734</v>
       </c>
       <c r="F22" t="n">
-        <v>-1.6736</v>
+        <v>-0.227</v>
       </c>
       <c r="G22" t="n">
-        <v>-1.4312</v>
+        <v>0.2848</v>
       </c>
       <c r="H22" t="n">
-        <v>-1.0123</v>
+        <v>1.1484</v>
       </c>
       <c r="I22" t="n">
-        <v>-0.4189</v>
+        <v>-0.8636</v>
       </c>
       <c r="J22" t="n">
-        <v>0.4117</v>
+        <v>2.6674</v>
       </c>
       <c r="K22" t="n">
-        <v>0.2903</v>
+        <v>2.0466</v>
       </c>
       <c r="L22" t="n">
-        <v>0.1214</v>
+        <v>0.6208</v>
       </c>
       <c r="M22" t="n">
-        <v>-1.8429</v>
+        <v>-2.3826</v>
       </c>
       <c r="N22" t="n">
-        <v>-1.3026</v>
+        <v>-0.8982</v>
       </c>
       <c r="O22" t="n">
-        <v>-0.5403</v>
+        <v>-1.4844</v>
       </c>
       <c r="P22" t="n">
-        <v>-1.1721</v>
+        <v>-4.4929</v>
       </c>
       <c r="Q22" t="n">
-        <v>-1.9534</v>
+        <v>-5.8603</v>
       </c>
       <c r="R22" t="n">
-        <v>0.7814</v>
+        <v>1.3674</v>
       </c>
       <c r="S22" t="n">
-        <v>0.7023</v>
+        <v>0.4932</v>
       </c>
       <c r="T22" t="n">
-        <v>0.09569999999999999</v>
+        <v>-0.295</v>
       </c>
       <c r="U22" t="n">
-        <v>0.6066</v>
+        <v>0.7882</v>
       </c>
       <c r="V22" t="n">
-        <v>-1.2186</v>
+        <v>2.7145</v>
       </c>
       <c r="W22" t="n">
-        <v>0</v>
+        <v>2.7145</v>
       </c>
       <c r="X22" t="n">
-        <v>-1.2186</v>
+        <v>0</v>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>play_by_play_2484313_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>--- TOTAL ---</t>
+          <t>P. CABANERO PUERTAS</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2203,68 +2309,235 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
+        <v>-1.5837</v>
+      </c>
+      <c r="E23" t="n">
+        <v>-1.5144</v>
+      </c>
+      <c r="F23" t="n">
+        <v>-0.0693</v>
+      </c>
+      <c r="G23" t="n">
+        <v>-1.7441</v>
+      </c>
+      <c r="H23" t="n">
+        <v>-0.2865</v>
+      </c>
+      <c r="I23" t="n">
+        <v>-1.4576</v>
+      </c>
+      <c r="J23" t="n">
+        <v>0.3089</v>
+      </c>
+      <c r="K23" t="n">
+        <v>0.8212</v>
+      </c>
+      <c r="L23" t="n">
+        <v>-0.5122</v>
+      </c>
+      <c r="M23" t="n">
+        <v>-2.053</v>
+      </c>
+      <c r="N23" t="n">
+        <v>-1.1077</v>
+      </c>
+      <c r="O23" t="n">
+        <v>-0.9453</v>
+      </c>
+      <c r="P23" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q23" t="n">
+        <v>-1.9534</v>
+      </c>
+      <c r="R23" t="n">
+        <v>1.9534</v>
+      </c>
+      <c r="S23" t="n">
+        <v>0.7697000000000001</v>
+      </c>
+      <c r="T23" t="n">
+        <v>0.1301</v>
+      </c>
+      <c r="U23" t="n">
+        <v>0.6395999999999999</v>
+      </c>
+      <c r="V23" t="n">
+        <v>-0.6093</v>
+      </c>
+      <c r="W23" t="n">
+        <v>0</v>
+      </c>
+      <c r="X23" t="n">
+        <v>-0.6093</v>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>play_by_play_2484313_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>F. VIDAL RAMOS</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>FRIVALCA LA MUELA</t>
+        </is>
+      </c>
+      <c r="C24" t="n">
+        <v>1</v>
+      </c>
+      <c r="D24" t="n">
+        <v>-3.1196</v>
+      </c>
+      <c r="E24" t="n">
+        <v>-1.446</v>
+      </c>
+      <c r="F24" t="n">
+        <v>-1.6736</v>
+      </c>
+      <c r="G24" t="n">
+        <v>-1.4312</v>
+      </c>
+      <c r="H24" t="n">
+        <v>-1.0123</v>
+      </c>
+      <c r="I24" t="n">
+        <v>-0.4189</v>
+      </c>
+      <c r="J24" t="n">
+        <v>0.4117</v>
+      </c>
+      <c r="K24" t="n">
+        <v>0.2903</v>
+      </c>
+      <c r="L24" t="n">
+        <v>0.1214</v>
+      </c>
+      <c r="M24" t="n">
+        <v>-1.8429</v>
+      </c>
+      <c r="N24" t="n">
+        <v>-1.3026</v>
+      </c>
+      <c r="O24" t="n">
+        <v>-0.5403</v>
+      </c>
+      <c r="P24" t="n">
+        <v>-1.1721</v>
+      </c>
+      <c r="Q24" t="n">
+        <v>-1.9534</v>
+      </c>
+      <c r="R24" t="n">
+        <v>0.7814</v>
+      </c>
+      <c r="S24" t="n">
+        <v>0.7023</v>
+      </c>
+      <c r="T24" t="n">
+        <v>0.09569999999999999</v>
+      </c>
+      <c r="U24" t="n">
+        <v>0.6066</v>
+      </c>
+      <c r="V24" t="n">
+        <v>-1.2186</v>
+      </c>
+      <c r="W24" t="n">
+        <v>0</v>
+      </c>
+      <c r="X24" t="n">
+        <v>-1.2186</v>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>play_by_play_2484313_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>--- TOTAL ---</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>FRIVALCA LA MUELA</t>
+        </is>
+      </c>
+      <c r="C25" t="n">
+        <v>1</v>
+      </c>
+      <c r="D25" t="n">
         <v>10.3959</v>
       </c>
-      <c r="E23" t="n">
+      <c r="E25" t="n">
         <v>8.655000000000001</v>
       </c>
-      <c r="F23" t="n">
+      <c r="F25" t="n">
         <v>1.7409</v>
       </c>
-      <c r="G23" t="n">
+      <c r="G25" t="n">
         <v>5.439400000000001</v>
       </c>
-      <c r="H23" t="n">
-        <v>2.744800000000001</v>
-      </c>
-      <c r="I23" t="n">
-        <v>2.694400000000001</v>
-      </c>
-      <c r="J23" t="n">
+      <c r="H25" t="n">
+        <v>2.7448</v>
+      </c>
+      <c r="I25" t="n">
+        <v>2.6944</v>
+      </c>
+      <c r="J25" t="n">
         <v>17.1264</v>
       </c>
-      <c r="K23" t="n">
+      <c r="K25" t="n">
         <v>11.7268</v>
       </c>
-      <c r="L23" t="n">
-        <v>5.3997</v>
-      </c>
-      <c r="M23" t="n">
+      <c r="L25" t="n">
+        <v>5.399800000000001</v>
+      </c>
+      <c r="M25" t="n">
         <v>-11.687</v>
       </c>
-      <c r="N23" t="n">
+      <c r="N25" t="n">
         <v>-8.9818</v>
       </c>
-      <c r="O23" t="n">
+      <c r="O25" t="n">
         <v>-2.7052</v>
       </c>
-      <c r="P23" t="n">
-        <v>-5.860300000000001</v>
-      </c>
-      <c r="Q23" t="n">
+      <c r="P25" t="n">
+        <v>-5.860299999999999</v>
+      </c>
+      <c r="Q25" t="n">
         <v>-19.5341</v>
       </c>
-      <c r="R23" t="n">
+      <c r="R25" t="n">
         <v>13.674</v>
       </c>
-      <c r="S23" t="n">
+      <c r="S25" t="n">
         <v>8.047499999999999</v>
       </c>
-      <c r="T23" t="n">
+      <c r="T25" t="n">
         <v>2.6421</v>
       </c>
-      <c r="U23" t="n">
+      <c r="U25" t="n">
         <v>5.4054</v>
       </c>
-      <c r="V23" t="n">
-        <v>2.769300000000001</v>
-      </c>
-      <c r="W23" t="n">
+      <c r="V25" t="n">
+        <v>2.7693</v>
+      </c>
+      <c r="W25" t="n">
         <v>8.4207</v>
       </c>
-      <c r="X23" t="n">
-        <v>-5.651299999999999</v>
-      </c>
+      <c r="X25" t="n">
+        <v>-5.651300000000001</v>
+      </c>
+      <c r="Y25" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
